--- a/docs/OMS_TestCases_BVA_EP_EN.xlsx
+++ b/docs/OMS_TestCases_BVA_EP_EN.xlsx
@@ -1,23 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STUDY\SWIN\Lab\JDA\llmagent4code\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30058A12-0915-4A7B-8BD0-23F5600E0EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="10236" yWindow="0" windowWidth="12900" windowHeight="13776" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Customer" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Product" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Order" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Payment" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Invoice" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Customer" sheetId="3" r:id="rId3"/>
+    <sheet name="Product" sheetId="4" r:id="rId4"/>
+    <sheet name="Order" sheetId="5" r:id="rId5"/>
+    <sheet name="Payment" sheetId="6" r:id="rId6"/>
+    <sheet name="Invoice" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -28,1914 +44,1910 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="633">
   <si>
-    <t xml:space="preserve">OMS - Test Case Suite (BVA + EP) - Derived from Domain Model Field Constraint Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: Field Constraint Table (Domain Model constraints for BVA/EP test design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meaning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Case ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format: TC_&lt;ENTITY&gt;_&lt;ATTRIBUTE&gt;_&lt;SEQ&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain entity under test (Customer, Product, Order, Payment, Invoice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field under test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design technique used: BVA (Boundary Value Analysis) or EP (Equivalence Partitioning)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equivalence Class / Boundary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For EP: class label, e.g. EC-Valid-1, EC-Invalid-1 (Empty), EC-Invalid-2 (Wrong Type). For BVA: boundary label, e.g. BC-Min-1, BC-Min, BC-Max, BC-Max+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Objective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short description of what the test case verifies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete value supplied to the attribute under test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions (other fields assumed valid)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other request fields assumed valid so this test isolates the attribute under test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected business-level outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected HTTP Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected HTTP status code: 2xx for valid classes, 4xx for invalid classes (exact code to be confirmed against the API error contract)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High / Medium / Low, carried over from the Field Constraint Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leave blank; fill Pass/Fail during execution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional notes, e.g. FK dependency, cross-field rule, semantic rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BVA/EP Convention used in this workbook:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- EP: each attribute is partitioned into valid and invalid equivalence classes. Each class is represented by exactly one representative test case (per standard EP practice).</t>
+    <t>OMS - Test Case Suite (BVA + EP) - Derived from Domain Model Field Constraint Table</t>
+  </si>
+  <si>
+    <t>Source: Field Constraint Table (Domain Model constraints for BVA/EP test design)</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Format: TC_&lt;ENTITY&gt;_&lt;ATTRIBUTE&gt;_&lt;SEQ&gt;</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Domain entity under test (Customer, Product, Order, Payment, Invoice)</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Field under test</t>
+  </si>
+  <si>
+    <t>Test Basis</t>
+  </si>
+  <si>
+    <t>Design technique used: BVA (Boundary Value Analysis) or EP (Equivalence Partitioning)</t>
+  </si>
+  <si>
+    <t>Equivalence Class / Boundary</t>
+  </si>
+  <si>
+    <t>For EP: class label, e.g. EC-Valid-1, EC-Invalid-1 (Empty), EC-Invalid-2 (Wrong Type). For BVA: boundary label, e.g. BC-Min-1, BC-Min, BC-Max, BC-Max+1</t>
+  </si>
+  <si>
+    <t>Test Objective</t>
+  </si>
+  <si>
+    <t>Short description of what the test case verifies</t>
+  </si>
+  <si>
+    <t>Input Value</t>
+  </si>
+  <si>
+    <t>Concrete value supplied to the attribute under test</t>
+  </si>
+  <si>
+    <t>Preconditions (other fields assumed valid)</t>
+  </si>
+  <si>
+    <t>Other request fields assumed valid so this test isolates the attribute under test</t>
+  </si>
+  <si>
+    <t>Expected Output</t>
+  </si>
+  <si>
+    <t>Expected business-level outcome</t>
+  </si>
+  <si>
+    <t>Expected HTTP Status</t>
+  </si>
+  <si>
+    <t>Expected HTTP status code: 2xx for valid classes, 4xx for invalid classes (exact code to be confirmed against the API error contract)</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>High / Medium / Low, carried over from the Field Constraint Table</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Leave blank; fill Pass/Fail during execution</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Additional notes, e.g. FK dependency, cross-field rule, semantic rule</t>
+  </si>
+  <si>
+    <t>BVA/EP Convention used in this workbook:</t>
+  </si>
+  <si>
+    <t>- EP: each attribute is partitioned into valid and invalid equivalence classes. Each class is represented by exactly one representative test case (per standard EP practice).</t>
   </si>
   <si>
     <t xml:space="preserve">  Class labels: EC-Valid-&lt;n&gt; for valid partitions, EC-Invalid-&lt;n&gt; (&lt;reason&gt;) for invalid partitions, e.g. EC-Invalid-1 (Empty), EC-Invalid-2 (Wrong Format), EC-Invalid-3 (Unsupported Value).</t>
   </si>
   <si>
-    <t xml:space="preserve">- BVA: applied only to attributes with a numeric or length boundary (min/max). Exactly 4 boundary points are tested per bounded attribute: BC-Min-1 (invalid), BC-Min (valid), BC-Max (valid), BC-Max+1 (invalid).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- BVA is NOT applied to enum, UUID/FK, or free-form unbounded fields; these are covered by EP only, consistent with standard test design theory.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Fields with cross-entity or workflow dependencies (computed totals, payment amount vs invoice amount, order status transitions) are flagged in Remarks; full coverage for these belongs to a separate Business Rule / State Transition table (Table B), not in scope of this file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Important notes:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- FK test cases (customerRef, productRef, orderRef, invoiceRef...) require seed data prior to execution (one valid existing record + one syntactically valid but non-existent UUID).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Cross-field / business rule test cases (computed totalAmount, payment.amount == invoice.totalAmount, state transitions) belong to Table B (Business Rule / State Transition table), not generated in this file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Date fields (dd/MM/yyyy) have two distinct invalid classes: wrong format (regex mismatch) and wrong semantic (non-existent calendar date, e.g. 31/02) - kept as separate test cases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Expected HTTP Status values are REST-convention defaults and must be reconciled with the actual API error contract once the backend is implemented.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Case Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Test Cases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ID_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Valid-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retrieve customer using a well-formed, existing UUID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;seed: existing customer id&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A - id is tested in isolation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returns the matching customer record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ID_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Not Found)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well-formed UUID that does not exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3fa85f64-5717-4562-b3fc-2c963f66afa6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer not found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ID_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Wrong Format)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malformed UUID string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not-a-uuid-123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected due to invalid format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ID_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-3 (Empty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty/null id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - id is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Min-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one below minimum (1 char)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address/phone/bankingDetails/role valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - below minimum length (&lt; 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at minimum (2 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer created successfully</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at maximum (100 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Max+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one above maximum (101 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum length (&gt; 100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordinary name with space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguyen Van A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Valid-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name containing hyphen/apostrophe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jean-Luc O'Brien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Empty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - name is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Digits Only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric-only string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - does not match name pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-3 (Symbols Only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Special characters only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@#$%^&amp;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_NAME_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-4 (Whitespace Only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whitespace-only string</t>
+    <t>- BVA: applied only to attributes with a numeric or length boundary (min/max). Exactly 4 boundary points are tested per bounded attribute: BC-Min-1 (invalid), BC-Min (valid), BC-Max (valid), BC-Max+1 (invalid).</t>
+  </si>
+  <si>
+    <t>- BVA is NOT applied to enum, UUID/FK, or free-form unbounded fields; these are covered by EP only, consistent with standard test design theory.</t>
+  </si>
+  <si>
+    <t>- Fields with cross-entity or workflow dependencies (computed totals, payment amount vs invoice amount, order status transitions) are flagged in Remarks; full coverage for these belongs to a separate Business Rule / State Transition table (Table B), not in scope of this file.</t>
+  </si>
+  <si>
+    <t>Important notes:</t>
+  </si>
+  <si>
+    <t>- FK test cases (customerRef, productRef, orderRef, invoiceRef...) require seed data prior to execution (one valid existing record + one syntactically valid but non-existent UUID).</t>
+  </si>
+  <si>
+    <t>- Cross-field / business rule test cases (computed totalAmount, payment.amount == invoice.totalAmount, state transitions) belong to Table B (Business Rule / State Transition table), not generated in this file.</t>
+  </si>
+  <si>
+    <t>- Date fields (dd/MM/yyyy) have two distinct invalid classes: wrong format (regex mismatch) and wrong semantic (non-existent calendar date, e.g. 31/02) - kept as separate test cases.</t>
+  </si>
+  <si>
+    <t>- Expected HTTP Status values are REST-convention defaults and must be reconciled with the actual API error contract once the backend is implemented.</t>
+  </si>
+  <si>
+    <t>Test Case Summary</t>
+  </si>
+  <si>
+    <t>Total Test Cases</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>EP</t>
+  </si>
+  <si>
+    <t>High Priority</t>
+  </si>
+  <si>
+    <t>Medium Priority</t>
+  </si>
+  <si>
+    <t>Low Priority</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>TC_CUS_ID_01</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>EC-Valid-1</t>
+  </si>
+  <si>
+    <t>Retrieve customer using a well-formed, existing UUID</t>
+  </si>
+  <si>
+    <t>&lt;seed: existing customer id&gt;</t>
+  </si>
+  <si>
+    <t>N/A - id is tested in isolation</t>
+  </si>
+  <si>
+    <t>Returns the matching customer record</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>TC_CUS_ID_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Not Found)</t>
+  </si>
+  <si>
+    <t>Well-formed UUID that does not exist</t>
+  </si>
+  <si>
+    <t>3fa85f64-5717-4562-b3fc-2c963f66afa6</t>
+  </si>
+  <si>
+    <t>Customer not found</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>TC_CUS_ID_03</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Wrong Format)</t>
+  </si>
+  <si>
+    <t>Malformed UUID string</t>
+  </si>
+  <si>
+    <t>not-a-uuid-123</t>
+  </si>
+  <si>
+    <t>Rejected due to invalid format</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>TC_CUS_ID_04</t>
+  </si>
+  <si>
+    <t>EC-Invalid-3 (Empty)</t>
+  </si>
+  <si>
+    <t>Empty/null id</t>
+  </si>
+  <si>
+    <t>Rejected - id is required</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_01</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>BC-Min-1</t>
+  </si>
+  <si>
+    <t>Length one below minimum (1 char)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>address/phone/bankingDetails/role valid</t>
+  </si>
+  <si>
+    <t>Rejected - below minimum length (&lt; 2)</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_02</t>
+  </si>
+  <si>
+    <t>BC-Min</t>
+  </si>
+  <si>
+    <t>Length at minimum (2 chars)</t>
+  </si>
+  <si>
+    <t>An</t>
+  </si>
+  <si>
+    <t>Customer created successfully</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_03</t>
+  </si>
+  <si>
+    <t>BC-Max</t>
+  </si>
+  <si>
+    <t>Length at maximum (100 chars)</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_04</t>
+  </si>
+  <si>
+    <t>BC-Max+1</t>
+  </si>
+  <si>
+    <t>Length one above maximum (101 chars)</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum length (&gt; 100)</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_05</t>
+  </si>
+  <si>
+    <t>Ordinary name with space</t>
+  </si>
+  <si>
+    <t>Nguyen Van A</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_06</t>
+  </si>
+  <si>
+    <t>EC-Valid-2</t>
+  </si>
+  <si>
+    <t>Name containing hyphen/apostrophe</t>
+  </si>
+  <si>
+    <t>Jean-Luc O'Brien</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_07</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Empty)</t>
+  </si>
+  <si>
+    <t>Empty string</t>
+  </si>
+  <si>
+    <t>Rejected - name is required</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_08</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Digits Only)</t>
+  </si>
+  <si>
+    <t>Numeric-only string</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>Rejected - does not match name pattern</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_09</t>
+  </si>
+  <si>
+    <t>EC-Invalid-3 (Symbols Only)</t>
+  </si>
+  <si>
+    <t>Special characters only</t>
+  </si>
+  <si>
+    <t>@#$%^&amp;</t>
+  </si>
+  <si>
+    <t>TC_CUS_NAME_10</t>
+  </si>
+  <si>
+    <t>EC-Invalid-4 (Whitespace Only)</t>
+  </si>
+  <si>
+    <t>Whitespace-only string</t>
   </si>
   <si>
     <t xml:space="preserve">     </t>
   </si>
   <si>
-    <t xml:space="preserve">Rejected - blank after trim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ADDRESS_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one below minimum (4 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name/phone/bankingDetails/role valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - below minimum length (&lt; 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ADDRESS_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at minimum (5 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ADDRESS_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at maximum (255 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ADDRESS_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one above maximum (256 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum length (&gt; 255)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ADDRESS_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - address is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ADDRESS_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Whitespace Only)</t>
+    <t>Rejected - blank after trim</t>
+  </si>
+  <si>
+    <t>TC_CUS_ADDRESS_01</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>Length one below minimum (4 chars)</t>
+  </si>
+  <si>
+    <t>12 A</t>
+  </si>
+  <si>
+    <t>name/phone/bankingDetails/role valid</t>
+  </si>
+  <si>
+    <t>Rejected - below minimum length (&lt; 5)</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_CUS_ADDRESS_02</t>
+  </si>
+  <si>
+    <t>Length at minimum (5 chars)</t>
+  </si>
+  <si>
+    <t>TC_CUS_ADDRESS_03</t>
+  </si>
+  <si>
+    <t>Length at maximum (255 chars)</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>TC_CUS_ADDRESS_04</t>
+  </si>
+  <si>
+    <t>Length one above maximum (256 chars)</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum length (&gt; 255)</t>
+  </si>
+  <si>
+    <t>TC_CUS_ADDRESS_05</t>
+  </si>
+  <si>
+    <t>Rejected - address is required</t>
+  </si>
+  <si>
+    <t>TC_CUS_ADDRESS_06</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Whitespace Only)</t>
   </si>
   <si>
     <t xml:space="preserve">        </t>
   </si>
   <si>
-    <t xml:space="preserve">TC_CUS_ADDRESS_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordinary full address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Nguyen Trai, Thanh Xuan, Hanoi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digit count one below minimum (7 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+8412345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name/address/bankingDetails/role valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - below minimum length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digit count at minimum (8 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+84912345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digit count at maximum (15 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+841234567890123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digit count one above maximum (16 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+8412345678901234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.164 without leading +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84912345678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Contains Letters)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alphanumeric mix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+849abc45678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - does not match pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Leading Zero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starts with 0 after country code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+8401234567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - violates semantic rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_PHONE_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty/null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - phone is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKACCTNU_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bankingDetails.accountNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one below minimum (5 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name/address/phone/bankName/role valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - below minimum length (&lt; 6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKACCTNU_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at minimum (6 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKACCTNU_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at maximum (20 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11111111111111111111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKACCTNU_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one above maximum (21 digits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111111111111111111111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum length (&gt; 20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKACCTNU_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12ab56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - must be numeric only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKACCTNU_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Empty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - accountNumber is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKNAME_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bankingDetails.bankName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name/address/phone/accountNumber/role valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKNAME_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKNAME_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKNAME_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKNAME_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - bankName is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_BANKNAME_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realistic bank name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vietcombank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ROLE_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid role - CUSTOMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUSTOMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name/address/phone/bankingDetails valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer created with role CUSTOMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ROLE_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid role - ORDER_STAFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORDER_STAFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer created with role ORDER_STAFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ROLE_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Valid-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid role - ACCOUNTANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACCOUNTANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer created with role ACCOUNTANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ROLE_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Unknown Value)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value not part of enum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANAGER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invalid enum value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ROLE_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Wrong Case)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowercase value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invalid enum value (case-sensitive)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ROLE_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - role is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ORDERHIST_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderHistory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty array (newly created customer, no orders yet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name/address/phone/bankingDetails/role valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer created successfully, orderHistory empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field is read-only / server-derived</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ORDERHIST_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Malformed Item)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Array containing a malformed UUID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">["not-a-uuid"]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected, or field ignored (read-only, not client-settable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_CUS_ORDERHIST_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Client-Supplied Read-Only Field)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client attempts to set a read-only field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">["3fa85f64-..."]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System ignores or rejects client-supplied value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_ID_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retrieve product using a well-formed, existing UUID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;seed: existing product id&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returns the matching product record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_ID_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product not found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_ID_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prod-123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_DESCRIPTIO_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one below minimum (2 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price.amount/price.currency valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - below minimum length (&lt; 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_DESCRIPTIO_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at minimum (3 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product created successfully</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_DESCRIPTIO_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length at maximum (500 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_DESCRIPTIO_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length one above maximum (501 chars)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum length (&gt; 500)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_DESCRIPTIO_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - description is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_DESCRIPTIO_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_DESCRIPTIO_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordinary product description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logitech M185 Wireless Mouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price.amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value below minimum boundary (0.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description/price.currency valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - must be greater than 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at minimum (0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at maximum (999999.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">999999.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value above maximum (1000000.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000000.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Negative)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - negative value not allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Wrong Decimal Precision)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More than 2 decimal places</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invalid decimal format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-3 (Non-Numeric)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-numeric string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invalid data type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_PRICEAMT_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-4 (Empty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - price.amount is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_CURRENCY_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price.currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supported currency - USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description/price.amount valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_CURRENCY_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supported currency - VND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_CURRENCY_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supported currency - EUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_CURRENCY_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Length-Mismatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length below fixed length (2 chars, also invalid code)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invalid length/not in supported list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_CURRENCY_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Unsupported Code)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well-formed 3-letter code not in supported list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XYZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - unsupported currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_CURRENCY_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">usd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - does not match ^[A-Z]{3}$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PRO_CURRENCY_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - price.currency is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_CUSTREF_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customerRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existing, valid customerRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lineItems valid (&gt;=1 item)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order created successfully</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_CUSTREF_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - customer not found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_CUSTREF_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cust-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invalid format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_CUSTREF_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - customerRef is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_LINEITEMS_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lineItems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item count one below minimum (0 items)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customerRef valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - order must contain at least 1 item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business rule to be confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_LINEITEMS_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item count at minimum (1 item)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{productRef, quantity:1}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_LINEITEMS_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item count at maximum (100 items)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[100 distinct productRef items]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_LINEITEMS_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item count one above maximum (101 items)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[101 items]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum item count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_LINEITEMS_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Non-Existent Product)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item references a non-existent product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{productRef: &lt;not-exist-uuid&gt;, quantity:1}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - product not found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_LINEITEMS_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Missing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lineItems null/missing entirely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - lineItems is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_LINEITEMS_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-3 (Duplicate Product)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two items reference the same productRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{productRef:P1,qty:1},{productRef:P1,qty:2}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected, or merged per business rule (to be confirmed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400/201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_QTY_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lineItems[].quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value one below minimum (0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">productRef valid, other order fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - quantity must be &gt;= 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_QTY_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at minimum (1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_QTY_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at maximum (1000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_QTY_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value one above maximum (1001)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - exceeds maximum quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_QTY_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_QTY_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Decimal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-integer value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - must be a whole number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_QTY_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-numeric value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_UNITPRICE_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lineItems[].unitPriceSnapshot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client omits price; server derives snapshot from current Product price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A - server-computed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">productRef valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server snapshots current product price correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field should be server-computed, not client-supplied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_UNITPRICE_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Tampered Value)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client supplies a price different from current Product price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (while Product is priced at 100.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected, or server-side value used instead of client value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_TOTALAMT_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totalAmount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server correctly computes total = sum(quantity * unitPrice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lineItems valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returned totalAmount matches computed sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server-computed field; see Table B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_TOTALAMT_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Client-Supplied Mismatch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client supplies a totalAmount different from the computed value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">999999.99 (incorrect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected, or value ignored and recomputed server-side</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_STATUS_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default status on creation is PLACED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLACED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customerRef/lineItems valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order created with status PLACED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full transition coverage in Table B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_STATUS_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Bypasses Workflow)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client sets status other than PLACED on creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHIPPED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - workflow cannot be bypassed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_STATUS_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Unknown Value)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_INVREF_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoiceRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoiceRef null prior to invoicing (e.g. PLACED/ACCEPTED)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">order in correct state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid - invoice not yet created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_INVREF_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoiceRef valid after invoice creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;seed: existing invoice id&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid - linked to invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ORD_INVREF_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoiceRef references a non-existent invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invoice not found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_ORDERREF_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef exists and order status is INVOICED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;seed: order status=INVOICED&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount/method valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment created successfully</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_ORDERREF_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Wrong State)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef exists but order status is not payable (e.g. PLACED)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;seed: order status=PLACED&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - order not in a payable state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_ORDERREF_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Not Found)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef does not exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - order not found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_ORDERREF_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-3 (Wrong Format)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">order-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_AMOUNT_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount exactly equals invoice.totalAmount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;seed: equal to invoice.totalAmount&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef/method valid, order already invoiced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment accepted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exact-match rule; partial payment policy to be confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_AMOUNT_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Underpayment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount less than invoice.totalAmount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoice.totalAmount - 0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - underpayment not accepted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_AMOUNT_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Overpayment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount greater than invoice.totalAmount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invoice.totalAmount + 0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - overpayment not accepted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_AMOUNT_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-3 (Zero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount equal to zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_AMOUNT_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-4 (Negative)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-50.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_AMOUNT_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-5 (Empty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - amount is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_STATUS_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default status on creation is PENDING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENDING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef/amount/method valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment created with status PENDING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_STATUS_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client sets status to VERIFIED on creation (bypassing accountant verification)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - cannot self-verify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_STATUS_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_METHOD_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid method - CREDIT_CARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CREDIT_CARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef/amount valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_METHOD_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid method - BANK_TRANSFER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANK_TRANSFER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_METHOD_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid method - E_WALLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E_WALLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_METHOD_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_METHOD_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - method is required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ORDERREF_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef exists and order status is ACCEPTED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;seed: order status=ACCEPTED&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">billingInfo/issueDate/dueDate valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice created successfully</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ORDERREF_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef exists but order status is not ACCEPTED (e.g. PLACED)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - order not yet accepted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ORDERREF_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_BILLNAME_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">billingInfo.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef valid, other fields valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapshot of Customer.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_BILLNAME_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_BILLNAME_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_BILLNAME_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_TOTALAMT_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server-computed totalAmount equals Order.totalAmount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totalAmount matches order.totalAmount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server-computed field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_TOTALAMT_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client supplies a totalAmount different from order.totalAmount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (incorrect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_TOTALAMT_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at zero boundary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ISSUEDATE_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">issueDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid date in dd/MM/yyyy format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format error vs semantic error kept separate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ISSUEDATE_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Wrong Separator)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uses hyphen instead of slash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-07-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - format regex mismatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ISSUEDATE_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Wrong Order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yyyy/MM/dd order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/07/23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ISSUEDATE_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-3 (Non-Existent Date)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well-formed but calendar-invalid date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/02/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - February does not have 31 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ISSUEDATE_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-4 (Non-Existent Date)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/02/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - February does not have 30 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ISSUEDATE_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Month-Min-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month value below minimum (0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/00/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - invalid month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_ISSUEDATE_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Month-Max+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month value above maximum (13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/13/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_DUEDATE_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dueDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dueDate = issueDate + 7 days (default)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/07/2026 (issueDate=23/07/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef/issueDate valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice created with default due date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depends on issueDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_DUEDATE_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC-Equal-Min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dueDate equals issueDate (0-day term, boundary equality)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/07/2026 (issueDate=23/07/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid - accepted since dueDate &gt;= issueDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_DUEDATE_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dueDate one day before issueDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/07/2026 (issueDate=23/07/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - dueDate cannot precede issueDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_DUEDATE_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-1 (Wrong Format)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISO format instead of dd/MM/yyyy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_DUEDATE_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-Invalid-2 (Non-Existent Date)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected - April does not have 31 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_STATUS_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default status on creation is ISSUED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISSUED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orderRef/billingInfo/issueDate/dueDate valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice created with status ISSUED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_STATUS_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client sets status other than ISSUED on creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_INV_STATUS_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRAFT</t>
+    <t>TC_CUS_ADDRESS_07</t>
+  </si>
+  <si>
+    <t>Ordinary full address</t>
+  </si>
+  <si>
+    <t>123 Nguyen Trai, Thanh Xuan, Hanoi</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_01</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>Digit count one below minimum (7 digits)</t>
+  </si>
+  <si>
+    <t>+8412345</t>
+  </si>
+  <si>
+    <t>name/address/bankingDetails/role valid</t>
+  </si>
+  <si>
+    <t>Rejected - below minimum length</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_02</t>
+  </si>
+  <si>
+    <t>Digit count at minimum (8 digits)</t>
+  </si>
+  <si>
+    <t>+84912345</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_03</t>
+  </si>
+  <si>
+    <t>Digit count at maximum (15 digits)</t>
+  </si>
+  <si>
+    <t>+841234567890123</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_04</t>
+  </si>
+  <si>
+    <t>Digit count one above maximum (16 digits)</t>
+  </si>
+  <si>
+    <t>+8412345678901234</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum length</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_05</t>
+  </si>
+  <si>
+    <t>E.164 without leading +</t>
+  </si>
+  <si>
+    <t>84912345678</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_06</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Contains Letters)</t>
+  </si>
+  <si>
+    <t>Alphanumeric mix</t>
+  </si>
+  <si>
+    <t>+849abc45678</t>
+  </si>
+  <si>
+    <t>Rejected - does not match pattern</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_07</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Leading Zero)</t>
+  </si>
+  <si>
+    <t>Starts with 0 after country code</t>
+  </si>
+  <si>
+    <t>+8401234567</t>
+  </si>
+  <si>
+    <t>Rejected - violates semantic rule</t>
+  </si>
+  <si>
+    <t>TC_CUS_PHONE_08</t>
+  </si>
+  <si>
+    <t>Empty/null</t>
+  </si>
+  <si>
+    <t>Rejected - phone is required</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKACCTNU_01</t>
+  </si>
+  <si>
+    <t>bankingDetails.accountNumber</t>
+  </si>
+  <si>
+    <t>Length one below minimum (5 digits)</t>
+  </si>
+  <si>
+    <t>name/address/phone/bankName/role valid</t>
+  </si>
+  <si>
+    <t>Rejected - below minimum length (&lt; 6)</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKACCTNU_02</t>
+  </si>
+  <si>
+    <t>Length at minimum (6 digits)</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKACCTNU_03</t>
+  </si>
+  <si>
+    <t>Length at maximum (20 digits)</t>
+  </si>
+  <si>
+    <t>11111111111111111111</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKACCTNU_04</t>
+  </si>
+  <si>
+    <t>Length one above maximum (21 digits)</t>
+  </si>
+  <si>
+    <t>111111111111111111111</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum length (&gt; 20)</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKACCTNU_05</t>
+  </si>
+  <si>
+    <t>12ab56</t>
+  </si>
+  <si>
+    <t>Rejected - must be numeric only</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKACCTNU_06</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Empty)</t>
+  </si>
+  <si>
+    <t>Rejected - accountNumber is required</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKNAME_01</t>
+  </si>
+  <si>
+    <t>bankingDetails.bankName</t>
+  </si>
+  <si>
+    <t>name/address/phone/accountNumber/role valid</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKNAME_02</t>
+  </si>
+  <si>
+    <t>VP</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKNAME_03</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKNAME_04</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKNAME_05</t>
+  </si>
+  <si>
+    <t>Rejected - bankName is required</t>
+  </si>
+  <si>
+    <t>TC_CUS_BANKNAME_06</t>
+  </si>
+  <si>
+    <t>Realistic bank name</t>
+  </si>
+  <si>
+    <t>Vietcombank</t>
+  </si>
+  <si>
+    <t>TC_CUS_ROLE_01</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>Valid role - CUSTOMER</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>name/address/phone/bankingDetails valid</t>
+  </si>
+  <si>
+    <t>Customer created with role CUSTOMER</t>
+  </si>
+  <si>
+    <t>TC_CUS_ROLE_02</t>
+  </si>
+  <si>
+    <t>Valid role - ORDER_STAFF</t>
+  </si>
+  <si>
+    <t>ORDER_STAFF</t>
+  </si>
+  <si>
+    <t>Customer created with role ORDER_STAFF</t>
+  </si>
+  <si>
+    <t>TC_CUS_ROLE_03</t>
+  </si>
+  <si>
+    <t>EC-Valid-3</t>
+  </si>
+  <si>
+    <t>Valid role - ACCOUNTANT</t>
+  </si>
+  <si>
+    <t>ACCOUNTANT</t>
+  </si>
+  <si>
+    <t>Customer created with role ACCOUNTANT</t>
+  </si>
+  <si>
+    <t>TC_CUS_ROLE_04</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Unknown Value)</t>
+  </si>
+  <si>
+    <t>Value not part of enum</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>Rejected - invalid enum value</t>
+  </si>
+  <si>
+    <t>TC_CUS_ROLE_05</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Wrong Case)</t>
+  </si>
+  <si>
+    <t>Lowercase value</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>Rejected - invalid enum value (case-sensitive)</t>
+  </si>
+  <si>
+    <t>TC_CUS_ROLE_06</t>
+  </si>
+  <si>
+    <t>Rejected - role is required</t>
+  </si>
+  <si>
+    <t>TC_CUS_ORDERHIST_01</t>
+  </si>
+  <si>
+    <t>orderHistory</t>
+  </si>
+  <si>
+    <t>Empty array (newly created customer, no orders yet)</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>name/address/phone/bankingDetails/role valid</t>
+  </si>
+  <si>
+    <t>Customer created successfully, orderHistory empty</t>
+  </si>
+  <si>
+    <t>Field is read-only / server-derived</t>
+  </si>
+  <si>
+    <t>TC_CUS_ORDERHIST_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Malformed Item)</t>
+  </si>
+  <si>
+    <t>Array containing a malformed UUID</t>
+  </si>
+  <si>
+    <t>["not-a-uuid"]</t>
+  </si>
+  <si>
+    <t>Rejected, or field ignored (read-only, not client-settable)</t>
+  </si>
+  <si>
+    <t>TC_CUS_ORDERHIST_03</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Client-Supplied Read-Only Field)</t>
+  </si>
+  <si>
+    <t>Client attempts to set a read-only field</t>
+  </si>
+  <si>
+    <t>["3fa85f64-..."]</t>
+  </si>
+  <si>
+    <t>System ignores or rejects client-supplied value</t>
+  </si>
+  <si>
+    <t>TC_PRO_ID_01</t>
+  </si>
+  <si>
+    <t>Retrieve product using a well-formed, existing UUID</t>
+  </si>
+  <si>
+    <t>&lt;seed: existing product id&gt;</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Returns the matching product record</t>
+  </si>
+  <si>
+    <t>TC_PRO_ID_02</t>
+  </si>
+  <si>
+    <t>Product not found</t>
+  </si>
+  <si>
+    <t>TC_PRO_ID_03</t>
+  </si>
+  <si>
+    <t>prod-123</t>
+  </si>
+  <si>
+    <t>TC_PRO_DESCRIPTIO_01</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Length one below minimum (2 chars)</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>price.amount/price.currency valid</t>
+  </si>
+  <si>
+    <t>Rejected - below minimum length (&lt; 3)</t>
+  </si>
+  <si>
+    <t>TC_PRO_DESCRIPTIO_02</t>
+  </si>
+  <si>
+    <t>Length at minimum (3 chars)</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>Product created successfully</t>
+  </si>
+  <si>
+    <t>TC_PRO_DESCRIPTIO_03</t>
+  </si>
+  <si>
+    <t>Length at maximum (500 chars)</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>TC_PRO_DESCRIPTIO_04</t>
+  </si>
+  <si>
+    <t>Length one above maximum (501 chars)</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum length (&gt; 500)</t>
+  </si>
+  <si>
+    <t>TC_PRO_DESCRIPTIO_05</t>
+  </si>
+  <si>
+    <t>Rejected - description is required</t>
+  </si>
+  <si>
+    <t>TC_PRO_DESCRIPTIO_06</t>
+  </si>
+  <si>
+    <t>TC_PRO_DESCRIPTIO_07</t>
+  </si>
+  <si>
+    <t>Ordinary product description</t>
+  </si>
+  <si>
+    <t>Logitech M185 Wireless Mouse</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_01</t>
+  </si>
+  <si>
+    <t>price.amount</t>
+  </si>
+  <si>
+    <t>Value below minimum boundary (0.00)</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>description/price.currency valid</t>
+  </si>
+  <si>
+    <t>Rejected - must be greater than 0</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_02</t>
+  </si>
+  <si>
+    <t>Value at minimum (0.01)</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_03</t>
+  </si>
+  <si>
+    <t>Value at maximum (999999.99)</t>
+  </si>
+  <si>
+    <t>999999.99</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_04</t>
+  </si>
+  <si>
+    <t>Value above maximum (1000000.00)</t>
+  </si>
+  <si>
+    <t>1000000.00</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum value</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_05</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Negative)</t>
+  </si>
+  <si>
+    <t>Negative value</t>
+  </si>
+  <si>
+    <t>-10.00</t>
+  </si>
+  <si>
+    <t>Rejected - negative value not allowed</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_06</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Wrong Decimal Precision)</t>
+  </si>
+  <si>
+    <t>More than 2 decimal places</t>
+  </si>
+  <si>
+    <t>10.999</t>
+  </si>
+  <si>
+    <t>Rejected - invalid decimal format</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_07</t>
+  </si>
+  <si>
+    <t>EC-Invalid-3 (Non-Numeric)</t>
+  </si>
+  <si>
+    <t>Non-numeric string</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Rejected - invalid data type</t>
+  </si>
+  <si>
+    <t>TC_PRO_PRICEAMT_08</t>
+  </si>
+  <si>
+    <t>EC-Invalid-4 (Empty)</t>
+  </si>
+  <si>
+    <t>Rejected - price.amount is required</t>
+  </si>
+  <si>
+    <t>TC_PRO_CURRENCY_01</t>
+  </si>
+  <si>
+    <t>price.currency</t>
+  </si>
+  <si>
+    <t>Supported currency - USD</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>description/price.amount valid</t>
+  </si>
+  <si>
+    <t>TC_PRO_CURRENCY_02</t>
+  </si>
+  <si>
+    <t>Supported currency - VND</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>TC_PRO_CURRENCY_03</t>
+  </si>
+  <si>
+    <t>Supported currency - EUR</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>TC_PRO_CURRENCY_04</t>
+  </si>
+  <si>
+    <t>BC-Length-Mismatch</t>
+  </si>
+  <si>
+    <t>Length below fixed length (2 chars, also invalid code)</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Rejected - invalid length/not in supported list</t>
+  </si>
+  <si>
+    <t>TC_PRO_CURRENCY_05</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Unsupported Code)</t>
+  </si>
+  <si>
+    <t>Well-formed 3-letter code not in supported list</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>Rejected - unsupported currency</t>
+  </si>
+  <si>
+    <t>TC_PRO_CURRENCY_06</t>
+  </si>
+  <si>
+    <t>usd</t>
+  </si>
+  <si>
+    <t>Rejected - does not match ^[A-Z]{3}$</t>
+  </si>
+  <si>
+    <t>TC_PRO_CURRENCY_07</t>
+  </si>
+  <si>
+    <t>Rejected - price.currency is required</t>
+  </si>
+  <si>
+    <t>TC_ORD_CUSTREF_01</t>
+  </si>
+  <si>
+    <t>customerRef</t>
+  </si>
+  <si>
+    <t>Existing, valid customerRef</t>
+  </si>
+  <si>
+    <t>lineItems valid (&gt;=1 item)</t>
+  </si>
+  <si>
+    <t>Order created successfully</t>
+  </si>
+  <si>
+    <t>TC_ORD_CUSTREF_02</t>
+  </si>
+  <si>
+    <t>Rejected - customer not found</t>
+  </si>
+  <si>
+    <t>TC_ORD_CUSTREF_03</t>
+  </si>
+  <si>
+    <t>cust-1</t>
+  </si>
+  <si>
+    <t>Rejected - invalid format</t>
+  </si>
+  <si>
+    <t>TC_ORD_CUSTREF_04</t>
+  </si>
+  <si>
+    <t>Rejected - customerRef is required</t>
+  </si>
+  <si>
+    <t>TC_ORD_LINEITEMS_01</t>
+  </si>
+  <si>
+    <t>lineItems</t>
+  </si>
+  <si>
+    <t>Item count one below minimum (0 items)</t>
+  </si>
+  <si>
+    <t>customerRef valid</t>
+  </si>
+  <si>
+    <t>Rejected - order must contain at least 1 item</t>
+  </si>
+  <si>
+    <t>Business rule to be confirmed</t>
+  </si>
+  <si>
+    <t>TC_ORD_LINEITEMS_02</t>
+  </si>
+  <si>
+    <t>Item count at minimum (1 item)</t>
+  </si>
+  <si>
+    <t>[{productRef, quantity:1}]</t>
+  </si>
+  <si>
+    <t>TC_ORD_LINEITEMS_03</t>
+  </si>
+  <si>
+    <t>Item count at maximum (100 items)</t>
+  </si>
+  <si>
+    <t>[100 distinct productRef items]</t>
+  </si>
+  <si>
+    <t>TC_ORD_LINEITEMS_04</t>
+  </si>
+  <si>
+    <t>Item count one above maximum (101 items)</t>
+  </si>
+  <si>
+    <t>[101 items]</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum item count</t>
+  </si>
+  <si>
+    <t>TC_ORD_LINEITEMS_05</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Non-Existent Product)</t>
+  </si>
+  <si>
+    <t>Item references a non-existent product</t>
+  </si>
+  <si>
+    <t>[{productRef: &lt;not-exist-uuid&gt;, quantity:1}]</t>
+  </si>
+  <si>
+    <t>Rejected - product not found</t>
+  </si>
+  <si>
+    <t>TC_ORD_LINEITEMS_06</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Missing)</t>
+  </si>
+  <si>
+    <t>lineItems null/missing entirely</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Rejected - lineItems is required</t>
+  </si>
+  <si>
+    <t>TC_ORD_LINEITEMS_07</t>
+  </si>
+  <si>
+    <t>EC-Invalid-3 (Duplicate Product)</t>
+  </si>
+  <si>
+    <t>Two items reference the same productRef</t>
+  </si>
+  <si>
+    <t>[{productRef:P1,qty:1},{productRef:P1,qty:2}]</t>
+  </si>
+  <si>
+    <t>Rejected, or merged per business rule (to be confirmed)</t>
+  </si>
+  <si>
+    <t>400/201</t>
+  </si>
+  <si>
+    <t>TC_ORD_QTY_01</t>
+  </si>
+  <si>
+    <t>lineItems[].quantity</t>
+  </si>
+  <si>
+    <t>Value one below minimum (0)</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>productRef valid, other order fields valid</t>
+  </si>
+  <si>
+    <t>Rejected - quantity must be &gt;= 1</t>
+  </si>
+  <si>
+    <t>TC_ORD_QTY_02</t>
+  </si>
+  <si>
+    <t>Value at minimum (1)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>TC_ORD_QTY_03</t>
+  </si>
+  <si>
+    <t>Value at maximum (1000)</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>TC_ORD_QTY_04</t>
+  </si>
+  <si>
+    <t>Value one above maximum (1001)</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>Rejected - exceeds maximum quantity</t>
+  </si>
+  <si>
+    <t>TC_ORD_QTY_05</t>
+  </si>
+  <si>
+    <t>-5</t>
+  </si>
+  <si>
+    <t>TC_ORD_QTY_06</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Decimal)</t>
+  </si>
+  <si>
+    <t>Non-integer value</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Rejected - must be a whole number</t>
+  </si>
+  <si>
+    <t>TC_ORD_QTY_07</t>
+  </si>
+  <si>
+    <t>Non-numeric value</t>
+  </si>
+  <si>
+    <t>TC_ORD_UNITPRICE_01</t>
+  </si>
+  <si>
+    <t>lineItems[].unitPriceSnapshot</t>
+  </si>
+  <si>
+    <t>Client omits price; server derives snapshot from current Product price</t>
+  </si>
+  <si>
+    <t>N/A - server-computed</t>
+  </si>
+  <si>
+    <t>productRef valid</t>
+  </si>
+  <si>
+    <t>Server snapshots current product price correctly</t>
+  </si>
+  <si>
+    <t>Field should be server-computed, not client-supplied</t>
+  </si>
+  <si>
+    <t>TC_ORD_UNITPRICE_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Tampered Value)</t>
+  </si>
+  <si>
+    <t>Client supplies a price different from current Product price</t>
+  </si>
+  <si>
+    <t>0.01 (while Product is priced at 100.00)</t>
+  </si>
+  <si>
+    <t>Rejected, or server-side value used instead of client value</t>
+  </si>
+  <si>
+    <t>TC_ORD_TOTALAMT_01</t>
+  </si>
+  <si>
+    <t>totalAmount</t>
+  </si>
+  <si>
+    <t>Server correctly computes total = sum(quantity * unitPrice)</t>
+  </si>
+  <si>
+    <t>lineItems valid</t>
+  </si>
+  <si>
+    <t>Returned totalAmount matches computed sum</t>
+  </si>
+  <si>
+    <t>Server-computed field; see Table B</t>
+  </si>
+  <si>
+    <t>TC_ORD_TOTALAMT_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Client-Supplied Mismatch)</t>
+  </si>
+  <si>
+    <t>Client supplies a totalAmount different from the computed value</t>
+  </si>
+  <si>
+    <t>999999.99 (incorrect)</t>
+  </si>
+  <si>
+    <t>Rejected, or value ignored and recomputed server-side</t>
+  </si>
+  <si>
+    <t>TC_ORD_STATUS_01</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Default status on creation is PLACED</t>
+  </si>
+  <si>
+    <t>PLACED</t>
+  </si>
+  <si>
+    <t>customerRef/lineItems valid</t>
+  </si>
+  <si>
+    <t>Order created with status PLACED</t>
+  </si>
+  <si>
+    <t>Full transition coverage in Table B</t>
+  </si>
+  <si>
+    <t>TC_ORD_STATUS_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Bypasses Workflow)</t>
+  </si>
+  <si>
+    <t>Client sets status other than PLACED on creation</t>
+  </si>
+  <si>
+    <t>SHIPPED</t>
+  </si>
+  <si>
+    <t>Rejected - workflow cannot be bypassed</t>
+  </si>
+  <si>
+    <t>TC_ORD_STATUS_03</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Unknown Value)</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>TC_ORD_INVREF_01</t>
+  </si>
+  <si>
+    <t>invoiceRef</t>
+  </si>
+  <si>
+    <t>invoiceRef null prior to invoicing (e.g. PLACED/ACCEPTED)</t>
+  </si>
+  <si>
+    <t>order in correct state</t>
+  </si>
+  <si>
+    <t>Valid - invoice not yet created</t>
+  </si>
+  <si>
+    <t>TC_ORD_INVREF_02</t>
+  </si>
+  <si>
+    <t>invoiceRef valid after invoice creation</t>
+  </si>
+  <si>
+    <t>&lt;seed: existing invoice id&gt;</t>
+  </si>
+  <si>
+    <t>Valid - linked to invoice</t>
+  </si>
+  <si>
+    <t>TC_ORD_INVREF_03</t>
+  </si>
+  <si>
+    <t>invoiceRef references a non-existent invoice</t>
+  </si>
+  <si>
+    <t>Rejected - invoice not found</t>
+  </si>
+  <si>
+    <t>TC_PAY_ORDERREF_01</t>
+  </si>
+  <si>
+    <t>orderRef</t>
+  </si>
+  <si>
+    <t>orderRef exists and order status is INVOICED</t>
+  </si>
+  <si>
+    <t>&lt;seed: order status=INVOICED&gt;</t>
+  </si>
+  <si>
+    <t>amount/method valid</t>
+  </si>
+  <si>
+    <t>Payment created successfully</t>
+  </si>
+  <si>
+    <t>TC_PAY_ORDERREF_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Wrong State)</t>
+  </si>
+  <si>
+    <t>orderRef exists but order status is not payable (e.g. PLACED)</t>
+  </si>
+  <si>
+    <t>&lt;seed: order status=PLACED&gt;</t>
+  </si>
+  <si>
+    <t>Rejected - order not in a payable state</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>TC_PAY_ORDERREF_03</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Not Found)</t>
+  </si>
+  <si>
+    <t>orderRef does not exist</t>
+  </si>
+  <si>
+    <t>Rejected - order not found</t>
+  </si>
+  <si>
+    <t>TC_PAY_ORDERREF_04</t>
+  </si>
+  <si>
+    <t>EC-Invalid-3 (Wrong Format)</t>
+  </si>
+  <si>
+    <t>order-1</t>
+  </si>
+  <si>
+    <t>TC_PAY_AMOUNT_01</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>amount exactly equals invoice.totalAmount</t>
+  </si>
+  <si>
+    <t>&lt;seed: equal to invoice.totalAmount&gt;</t>
+  </si>
+  <si>
+    <t>orderRef/method valid, order already invoiced</t>
+  </si>
+  <si>
+    <t>Payment accepted</t>
+  </si>
+  <si>
+    <t>Exact-match rule; partial payment policy to be confirmed</t>
+  </si>
+  <si>
+    <t>TC_PAY_AMOUNT_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Underpayment)</t>
+  </si>
+  <si>
+    <t>amount less than invoice.totalAmount</t>
+  </si>
+  <si>
+    <t>invoice.totalAmount - 0.01</t>
+  </si>
+  <si>
+    <t>Rejected - underpayment not accepted</t>
+  </si>
+  <si>
+    <t>TC_PAY_AMOUNT_03</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Overpayment)</t>
+  </si>
+  <si>
+    <t>amount greater than invoice.totalAmount</t>
+  </si>
+  <si>
+    <t>invoice.totalAmount + 0.01</t>
+  </si>
+  <si>
+    <t>Rejected - overpayment not accepted</t>
+  </si>
+  <si>
+    <t>TC_PAY_AMOUNT_04</t>
+  </si>
+  <si>
+    <t>EC-Invalid-3 (Zero)</t>
+  </si>
+  <si>
+    <t>amount equal to zero</t>
+  </si>
+  <si>
+    <t>TC_PAY_AMOUNT_05</t>
+  </si>
+  <si>
+    <t>EC-Invalid-4 (Negative)</t>
+  </si>
+  <si>
+    <t>-50.00</t>
+  </si>
+  <si>
+    <t>TC_PAY_AMOUNT_06</t>
+  </si>
+  <si>
+    <t>EC-Invalid-5 (Empty)</t>
+  </si>
+  <si>
+    <t>Rejected - amount is required</t>
+  </si>
+  <si>
+    <t>TC_PAY_STATUS_01</t>
+  </si>
+  <si>
+    <t>Default status on creation is PENDING</t>
+  </si>
+  <si>
+    <t>PENDING</t>
+  </si>
+  <si>
+    <t>orderRef/amount/method valid</t>
+  </si>
+  <si>
+    <t>Payment created with status PENDING</t>
+  </si>
+  <si>
+    <t>TC_PAY_STATUS_02</t>
+  </si>
+  <si>
+    <t>Client sets status to VERIFIED on creation (bypassing accountant verification)</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>Rejected - cannot self-verify</t>
+  </si>
+  <si>
+    <t>TC_PAY_STATUS_03</t>
+  </si>
+  <si>
+    <t>TC_PAY_METHOD_01</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>Valid method - CREDIT_CARD</t>
+  </si>
+  <si>
+    <t>CREDIT_CARD</t>
+  </si>
+  <si>
+    <t>orderRef/amount valid</t>
+  </si>
+  <si>
+    <t>TC_PAY_METHOD_02</t>
+  </si>
+  <si>
+    <t>Valid method - BANK_TRANSFER</t>
+  </si>
+  <si>
+    <t>BANK_TRANSFER</t>
+  </si>
+  <si>
+    <t>TC_PAY_METHOD_03</t>
+  </si>
+  <si>
+    <t>Valid method - E_WALLET</t>
+  </si>
+  <si>
+    <t>E_WALLET</t>
+  </si>
+  <si>
+    <t>TC_PAY_METHOD_04</t>
+  </si>
+  <si>
+    <t>CASH</t>
+  </si>
+  <si>
+    <t>TC_PAY_METHOD_05</t>
+  </si>
+  <si>
+    <t>Rejected - method is required</t>
+  </si>
+  <si>
+    <t>TC_INV_ORDERREF_01</t>
+  </si>
+  <si>
+    <t>orderRef exists and order status is ACCEPTED</t>
+  </si>
+  <si>
+    <t>&lt;seed: order status=ACCEPTED&gt;</t>
+  </si>
+  <si>
+    <t>billingInfo/issueDate/dueDate valid</t>
+  </si>
+  <si>
+    <t>Invoice created successfully</t>
+  </si>
+  <si>
+    <t>TC_INV_ORDERREF_02</t>
+  </si>
+  <si>
+    <t>orderRef exists but order status is not ACCEPTED (e.g. PLACED)</t>
+  </si>
+  <si>
+    <t>Rejected - order not yet accepted</t>
+  </si>
+  <si>
+    <t>TC_INV_ORDERREF_03</t>
+  </si>
+  <si>
+    <t>TC_INV_BILLNAME_01</t>
+  </si>
+  <si>
+    <t>billingInfo.name</t>
+  </si>
+  <si>
+    <t>orderRef valid, other fields valid</t>
+  </si>
+  <si>
+    <t>Snapshot of Customer.name</t>
+  </si>
+  <si>
+    <t>TC_INV_BILLNAME_02</t>
+  </si>
+  <si>
+    <t>TC_INV_BILLNAME_03</t>
+  </si>
+  <si>
+    <t>TC_INV_BILLNAME_04</t>
+  </si>
+  <si>
+    <t>TC_INV_TOTALAMT_01</t>
+  </si>
+  <si>
+    <t>Server-computed totalAmount equals Order.totalAmount</t>
+  </si>
+  <si>
+    <t>orderRef valid</t>
+  </si>
+  <si>
+    <t>totalAmount matches order.totalAmount</t>
+  </si>
+  <si>
+    <t>Server-computed field</t>
+  </si>
+  <si>
+    <t>TC_INV_TOTALAMT_02</t>
+  </si>
+  <si>
+    <t>Client supplies a totalAmount different from order.totalAmount</t>
+  </si>
+  <si>
+    <t>0.01 (incorrect)</t>
+  </si>
+  <si>
+    <t>TC_INV_TOTALAMT_03</t>
+  </si>
+  <si>
+    <t>Value at zero boundary</t>
+  </si>
+  <si>
+    <t>TC_INV_ISSUEDATE_01</t>
+  </si>
+  <si>
+    <t>issueDate</t>
+  </si>
+  <si>
+    <t>Valid date in dd/MM/yyyy format</t>
+  </si>
+  <si>
+    <t>23/07/2026</t>
+  </si>
+  <si>
+    <t>Format error vs semantic error kept separate</t>
+  </si>
+  <si>
+    <t>TC_INV_ISSUEDATE_02</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Wrong Separator)</t>
+  </si>
+  <si>
+    <t>Uses hyphen instead of slash</t>
+  </si>
+  <si>
+    <t>23-07-2026</t>
+  </si>
+  <si>
+    <t>Rejected - format regex mismatch</t>
+  </si>
+  <si>
+    <t>TC_INV_ISSUEDATE_03</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Wrong Order)</t>
+  </si>
+  <si>
+    <t>yyyy/MM/dd order</t>
+  </si>
+  <si>
+    <t>2026/07/23</t>
+  </si>
+  <si>
+    <t>TC_INV_ISSUEDATE_04</t>
+  </si>
+  <si>
+    <t>EC-Invalid-3 (Non-Existent Date)</t>
+  </si>
+  <si>
+    <t>Well-formed but calendar-invalid date</t>
+  </si>
+  <si>
+    <t>31/02/2026</t>
+  </si>
+  <si>
+    <t>Rejected - February does not have 31 days</t>
+  </si>
+  <si>
+    <t>TC_INV_ISSUEDATE_05</t>
+  </si>
+  <si>
+    <t>EC-Invalid-4 (Non-Existent Date)</t>
+  </si>
+  <si>
+    <t>30/02/2026</t>
+  </si>
+  <si>
+    <t>Rejected - February does not have 30 days</t>
+  </si>
+  <si>
+    <t>TC_INV_ISSUEDATE_06</t>
+  </si>
+  <si>
+    <t>BC-Month-Min-1</t>
+  </si>
+  <si>
+    <t>Month value below minimum (0)</t>
+  </si>
+  <si>
+    <t>23/00/2026</t>
+  </si>
+  <si>
+    <t>Rejected - invalid month</t>
+  </si>
+  <si>
+    <t>TC_INV_ISSUEDATE_07</t>
+  </si>
+  <si>
+    <t>BC-Month-Max+1</t>
+  </si>
+  <si>
+    <t>Month value above maximum (13)</t>
+  </si>
+  <si>
+    <t>23/13/2026</t>
+  </si>
+  <si>
+    <t>TC_INV_DUEDATE_01</t>
+  </si>
+  <si>
+    <t>dueDate</t>
+  </si>
+  <si>
+    <t>dueDate = issueDate + 7 days (default)</t>
+  </si>
+  <si>
+    <t>30/07/2026 (issueDate=23/07/2026)</t>
+  </si>
+  <si>
+    <t>orderRef/issueDate valid</t>
+  </si>
+  <si>
+    <t>Invoice created with default due date</t>
+  </si>
+  <si>
+    <t>Depends on issueDate</t>
+  </si>
+  <si>
+    <t>TC_INV_DUEDATE_02</t>
+  </si>
+  <si>
+    <t>BC-Equal-Min</t>
+  </si>
+  <si>
+    <t>dueDate equals issueDate (0-day term, boundary equality)</t>
+  </si>
+  <si>
+    <t>23/07/2026 (issueDate=23/07/2026)</t>
+  </si>
+  <si>
+    <t>Valid - accepted since dueDate &gt;= issueDate</t>
+  </si>
+  <si>
+    <t>TC_INV_DUEDATE_03</t>
+  </si>
+  <si>
+    <t>dueDate one day before issueDate</t>
+  </si>
+  <si>
+    <t>22/07/2026 (issueDate=23/07/2026)</t>
+  </si>
+  <si>
+    <t>Rejected - dueDate cannot precede issueDate</t>
+  </si>
+  <si>
+    <t>TC_INV_DUEDATE_04</t>
+  </si>
+  <si>
+    <t>EC-Invalid-1 (Wrong Format)</t>
+  </si>
+  <si>
+    <t>ISO format instead of dd/MM/yyyy</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>TC_INV_DUEDATE_05</t>
+  </si>
+  <si>
+    <t>EC-Invalid-2 (Non-Existent Date)</t>
+  </si>
+  <si>
+    <t>31/04/2026</t>
+  </si>
+  <si>
+    <t>Rejected - April does not have 31 days</t>
+  </si>
+  <si>
+    <t>TC_INV_STATUS_01</t>
+  </si>
+  <si>
+    <t>Default status on creation is ISSUED</t>
+  </si>
+  <si>
+    <t>ISSUED</t>
+  </si>
+  <si>
+    <t>orderRef/billingInfo/issueDate/dueDate valid</t>
+  </si>
+  <si>
+    <t>Invoice created with status ISSUED</t>
+  </si>
+  <si>
+    <t>TC_INV_STATUS_02</t>
+  </si>
+  <si>
+    <t>Client sets status other than ISSUED on creation</t>
+  </si>
+  <si>
+    <t>PAID</t>
+  </si>
+  <si>
+    <t>TC_INV_STATUS_03</t>
+  </si>
+  <si>
+    <t>DRAFT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1944,71 +1956,54 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2033,16 +2028,28 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -2058,97 +2065,68 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2207,47 +2185,68 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5597"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFCE4EC"/>
+      <color rgb="FFE2EFDA"/>
+      <color rgb="FFFFCCCC"/>
+    </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2255,12 +2254,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2289,7 +2288,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2310,7 +2309,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2361,7 +2360,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2379,37 +2378,36 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2417,7 +2415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -2425,7 +2423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2433,7 +2431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -2441,7 +2439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -2449,7 +2447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
@@ -2457,7 +2455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
@@ -2465,7 +2463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
@@ -2473,7 +2471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
@@ -2481,7 +2479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
@@ -2489,7 +2487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
@@ -2497,7 +2495,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -2505,7 +2503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -2513,7 +2511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
@@ -2521,94 +2519,86 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:2" ht="58.2" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:2" ht="35.4" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2" ht="58.2" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2631,184 +2621,176 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="8">
         <v>50</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="8">
         <v>20</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="8">
         <v>30</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="8">
         <v>28</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="8">
         <v>13</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="8">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="8">
         <v>25</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="8">
         <v>9</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="8">
         <v>16</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="8">
         <v>18</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="8">
         <v>7</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="8">
         <v>28</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="8">
         <v>8</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="8">
         <v>20</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="8">
         <v>23</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="8">
         <v>5</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="8">
         <v>18</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="8">
         <v>0</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="8">
         <v>18</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="8">
         <v>13</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="8">
         <v>5</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="8">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="8">
         <v>9</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="8">
         <v>16</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="8">
         <v>9</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="8">
         <v>16</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="10" t="n">
-        <f aca="false">SUM(B4:B8)</f>
+      <c r="B9" s="10">
+        <f t="shared" ref="B9:G9" si="0">SUM(B4:B8)</f>
         <v>146</v>
       </c>
-      <c r="C9" s="10" t="n">
-        <f aca="false">SUM(C4:C8)</f>
+      <c r="C9" s="10">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <f aca="false">SUM(D4:D8)</f>
+      <c r="D9" s="10">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <f aca="false">SUM(E4:E8)</f>
+      <c r="E9" s="10">
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <f aca="false">SUM(F4:F8)</f>
+      <c r="F9" s="10">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="G9" s="10" t="n">
-        <f aca="false">SUM(G4:G8)</f>
+      <c r="G9" s="10">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M51"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="26"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -2849,7 +2831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>54</v>
       </c>
@@ -2886,7 +2868,7 @@
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>63</v>
       </c>
@@ -2923,7 +2905,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>69</v>
       </c>
@@ -2960,7 +2942,7 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>75</v>
       </c>
@@ -2995,155 +2977,155 @@
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="K6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="14"/>
+      <c r="M6" s="17"/>
+    </row>
+    <row r="7" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="K7" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+    </row>
+    <row r="8" spans="1:13" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="K8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" spans="1:13" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>101</v>
       </c>
@@ -3165,7 +3147,7 @@
       <c r="G10" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="21" t="s">
         <v>84</v>
       </c>
       <c r="I10" s="12" t="s">
@@ -3180,7 +3162,7 @@
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>104</v>
       </c>
@@ -3202,7 +3184,7 @@
       <c r="G11" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="21" t="s">
         <v>84</v>
       </c>
       <c r="I11" s="12" t="s">
@@ -3217,7 +3199,7 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>108</v>
       </c>
@@ -3237,7 +3219,7 @@
         <v>110</v>
       </c>
       <c r="G12" s="13"/>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="19" t="s">
         <v>84</v>
       </c>
       <c r="I12" s="13" t="s">
@@ -3252,7 +3234,7 @@
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>112</v>
       </c>
@@ -3274,7 +3256,7 @@
       <c r="G13" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="19" t="s">
         <v>84</v>
       </c>
       <c r="I13" s="13" t="s">
@@ -3289,7 +3271,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>117</v>
       </c>
@@ -3311,7 +3293,7 @@
       <c r="G14" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="19" t="s">
         <v>84</v>
       </c>
       <c r="I14" s="13" t="s">
@@ -3326,7 +3308,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>121</v>
       </c>
@@ -3348,7 +3330,7 @@
       <c r="G15" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="19" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="13" t="s">
@@ -3363,155 +3345,155 @@
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+    </row>
+    <row r="17" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+    </row>
+    <row r="18" spans="1:13" s="18" customFormat="1" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+    </row>
+    <row r="19" spans="1:13" s="15" customFormat="1" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+    </row>
+    <row r="20" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>142</v>
       </c>
@@ -3531,7 +3513,7 @@
         <v>110</v>
       </c>
       <c r="G20" s="13"/>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="19" t="s">
         <v>130</v>
       </c>
       <c r="I20" s="13" t="s">
@@ -3546,7 +3528,7 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>144</v>
       </c>
@@ -3565,10 +3547,10 @@
       <c r="F21" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="19" t="s">
         <v>130</v>
       </c>
       <c r="I21" s="13" t="s">
@@ -3583,7 +3565,7 @@
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>147</v>
       </c>
@@ -3605,7 +3587,7 @@
       <c r="G22" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="21" t="s">
         <v>130</v>
       </c>
       <c r="I22" s="12" t="s">
@@ -3620,155 +3602,155 @@
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="K23" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+    </row>
+    <row r="24" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="K24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+    </row>
+    <row r="25" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="K25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+    </row>
+    <row r="26" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+    </row>
+    <row r="27" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>166</v>
       </c>
@@ -3805,7 +3787,7 @@
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>169</v>
       </c>
@@ -3842,7 +3824,7 @@
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>174</v>
       </c>
@@ -3879,7 +3861,7 @@
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>179</v>
       </c>
@@ -3914,155 +3896,155 @@
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+    </row>
+    <row r="32" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="J32" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="K32" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+    </row>
+    <row r="33" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="J33" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K33" s="4" t="s">
+      <c r="K33" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+    </row>
+    <row r="34" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J34" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+    </row>
+    <row r="35" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>197</v>
       </c>
@@ -4099,7 +4081,7 @@
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>200</v>
       </c>
@@ -4134,155 +4116,155 @@
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I37" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="J37" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+    </row>
+    <row r="38" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J38" s="4" t="s">
+      <c r="J38" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+    </row>
+    <row r="39" spans="1:13" s="18" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A39" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J39" s="4" t="s">
+      <c r="J39" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="K39" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+    </row>
+    <row r="40" spans="1:13" s="15" customFormat="1" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="J40" s="4" t="s">
+      <c r="J40" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K40" s="4" t="s">
+      <c r="K40" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+    </row>
+    <row r="41" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>211</v>
       </c>
@@ -4317,7 +4299,7 @@
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>213</v>
       </c>
@@ -4354,7 +4336,7 @@
       <c r="L42" s="12"/>
       <c r="M42" s="12"/>
     </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
         <v>216</v>
       </c>
@@ -4391,7 +4373,7 @@
       <c r="L43" s="12"/>
       <c r="M43" s="12"/>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>222</v>
       </c>
@@ -4428,7 +4410,7 @@
       <c r="L44" s="12"/>
       <c r="M44" s="12"/>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4465,7 +4447,7 @@
       <c r="L45" s="12"/>
       <c r="M45" s="12"/>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>231</v>
       </c>
@@ -4502,7 +4484,7 @@
       <c r="L46" s="13"/>
       <c r="M46" s="13"/>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>236</v>
       </c>
@@ -4539,7 +4521,7 @@
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>241</v>
       </c>
@@ -4574,7 +4556,7 @@
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
     </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>243</v>
       </c>
@@ -4613,7 +4595,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>250</v>
       </c>
@@ -4652,7 +4634,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>255</v>
       </c>
@@ -4692,39 +4674,31 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="26"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -4765,7 +4739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>260</v>
       </c>
@@ -4802,7 +4776,7 @@
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>265</v>
       </c>
@@ -4839,7 +4813,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>267</v>
       </c>
@@ -4876,7 +4850,7 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>269</v>
       </c>
@@ -4913,7 +4887,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>275</v>
       </c>
@@ -4950,7 +4924,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:13" ht="330" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>279</v>
       </c>
@@ -4987,7 +4961,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:13" ht="343.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>282</v>
       </c>
@@ -5024,7 +4998,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>286</v>
       </c>
@@ -5059,7 +5033,7 @@
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>288</v>
       </c>
@@ -5096,7 +5070,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>289</v>
       </c>
@@ -5133,7 +5107,7 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>292</v>
       </c>
@@ -5170,7 +5144,7 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>298</v>
       </c>
@@ -5207,7 +5181,7 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>301</v>
       </c>
@@ -5244,7 +5218,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>304</v>
       </c>
@@ -5281,7 +5255,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>308</v>
       </c>
@@ -5318,7 +5292,7 @@
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>313</v>
       </c>
@@ -5355,7 +5329,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>318</v>
       </c>
@@ -5392,7 +5366,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>323</v>
       </c>
@@ -5427,7 +5401,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>326</v>
       </c>
@@ -5464,7 +5438,7 @@
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>331</v>
       </c>
@@ -5501,7 +5475,7 @@
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>334</v>
       </c>
@@ -5538,7 +5512,7 @@
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>337</v>
       </c>
@@ -5575,7 +5549,7 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>342</v>
       </c>
@@ -5612,7 +5586,7 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>347</v>
       </c>
@@ -5649,7 +5623,7 @@
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>350</v>
       </c>
@@ -5685,39 +5659,31 @@
       <c r="M26" s="13"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="26"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -5758,7 +5724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>352</v>
       </c>
@@ -5795,7 +5761,7 @@
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>357</v>
       </c>
@@ -5832,7 +5798,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>359</v>
       </c>
@@ -5869,7 +5835,7 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>362</v>
       </c>
@@ -5904,7 +5870,7 @@
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>364</v>
       </c>
@@ -5943,7 +5909,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>370</v>
       </c>
@@ -5982,7 +5948,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>373</v>
       </c>
@@ -6021,7 +5987,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>376</v>
       </c>
@@ -6060,7 +6026,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>380</v>
       </c>
@@ -6099,7 +6065,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>385</v>
       </c>
@@ -6138,7 +6104,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>390</v>
       </c>
@@ -6177,7 +6143,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>396</v>
       </c>
@@ -6214,7 +6180,7 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>402</v>
       </c>
@@ -6251,7 +6217,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>405</v>
       </c>
@@ -6288,7 +6254,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>408</v>
       </c>
@@ -6325,7 +6291,7 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>412</v>
       </c>
@@ -6362,7 +6328,7 @@
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>414</v>
       </c>
@@ -6399,7 +6365,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>419</v>
       </c>
@@ -6436,7 +6402,7 @@
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>421</v>
       </c>
@@ -6475,7 +6441,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>428</v>
       </c>
@@ -6514,7 +6480,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>433</v>
       </c>
@@ -6553,7 +6519,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>439</v>
       </c>
@@ -6592,7 +6558,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>444</v>
       </c>
@@ -6631,7 +6597,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>451</v>
       </c>
@@ -6670,7 +6636,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>456</v>
       </c>
@@ -6709,7 +6675,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>459</v>
       </c>
@@ -6746,7 +6712,7 @@
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>464</v>
       </c>
@@ -6783,7 +6749,7 @@
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>468</v>
       </c>
@@ -6821,39 +6787,31 @@
       <c r="M29" s="13"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="26"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -6894,7 +6852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>471</v>
       </c>
@@ -6931,7 +6889,7 @@
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>477</v>
       </c>
@@ -6968,7 +6926,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>483</v>
       </c>
@@ -7005,7 +6963,7 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>487</v>
       </c>
@@ -7042,7 +7000,7 @@
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>490</v>
       </c>
@@ -7081,7 +7039,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>497</v>
       </c>
@@ -7120,7 +7078,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>502</v>
       </c>
@@ -7159,7 +7117,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>507</v>
       </c>
@@ -7198,7 +7156,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>510</v>
       </c>
@@ -7237,7 +7195,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>513</v>
       </c>
@@ -7274,7 +7232,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>516</v>
       </c>
@@ -7311,7 +7269,7 @@
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
     </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>521</v>
       </c>
@@ -7348,7 +7306,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>525</v>
       </c>
@@ -7385,7 +7343,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>526</v>
       </c>
@@ -7422,7 +7380,7 @@
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>531</v>
       </c>
@@ -7459,7 +7417,7 @@
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>534</v>
       </c>
@@ -7496,7 +7454,7 @@
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>537</v>
       </c>
@@ -7533,7 +7491,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>539</v>
       </c>
@@ -7569,39 +7527,31 @@
       <c r="M19" s="13"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="26"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -7642,7 +7592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>541</v>
       </c>
@@ -7679,7 +7629,7 @@
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>546</v>
       </c>
@@ -7716,7 +7666,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>549</v>
       </c>
@@ -7753,7 +7703,7 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>550</v>
       </c>
@@ -7792,7 +7742,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>554</v>
       </c>
@@ -7831,7 +7781,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:13" ht="66" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>555</v>
       </c>
@@ -7870,7 +7820,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:13" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>556</v>
       </c>
@@ -7909,7 +7859,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>557</v>
       </c>
@@ -7948,7 +7898,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>562</v>
       </c>
@@ -7987,7 +7937,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>565</v>
       </c>
@@ -8026,7 +7976,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>567</v>
       </c>
@@ -8065,7 +8015,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>572</v>
       </c>
@@ -8104,7 +8054,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>577</v>
       </c>
@@ -8143,7 +8093,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>581</v>
       </c>
@@ -8182,7 +8132,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>586</v>
       </c>
@@ -8221,7 +8171,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>590</v>
       </c>
@@ -8260,7 +8210,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>595</v>
       </c>
@@ -8299,7 +8249,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>599</v>
       </c>
@@ -8338,7 +8288,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>606</v>
       </c>
@@ -8377,7 +8327,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>611</v>
       </c>
@@ -8416,7 +8366,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>615</v>
       </c>
@@ -8455,7 +8405,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>619</v>
       </c>
@@ -8494,7 +8444,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>623</v>
       </c>
@@ -8533,7 +8483,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>628</v>
       </c>
@@ -8572,7 +8522,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>631</v>
       </c>
@@ -8612,12 +8562,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/docs/OMS_TestCases_BVA_EP_EN.xlsx
+++ b/docs/OMS_TestCases_BVA_EP_EN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STUDY\SWIN\Lab\JDA\llmagent4code\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30058A12-0915-4A7B-8BD0-23F5600E0EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA783E4-FA95-40E6-AD4A-057D7B2B7635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10236" yWindow="0" windowWidth="12900" windowHeight="13776" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14088" yWindow="0" windowWidth="9048" windowHeight="13776" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -3051,7 +3051,7 @@
       <c r="L7" s="16"/>
       <c r="M7" s="16"/>
     </row>
-    <row r="8" spans="1:13" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>92</v>
       </c>
@@ -3419,7 +3419,7 @@
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
     </row>
-    <row r="18" spans="1:13" s="18" customFormat="1" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" s="18" customFormat="1" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>135</v>
       </c>
@@ -3456,7 +3456,7 @@
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
     </row>
-    <row r="19" spans="1:13" s="15" customFormat="1" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" s="15" customFormat="1" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>138</v>
       </c>
@@ -4850,153 +4850,153 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="6" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="330" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+    </row>
+    <row r="7" spans="1:13" s="18" customFormat="1" ht="330" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" ht="343.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+    </row>
+    <row r="8" spans="1:13" s="15" customFormat="1" ht="343.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
     </row>
     <row r="9" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
@@ -5107,153 +5107,153 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
     </row>
-    <row r="12" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="K12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+    </row>
+    <row r="13" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="K13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+    </row>
+    <row r="14" spans="1:13" s="18" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="K14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+    </row>
+    <row r="15" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="K15" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
     </row>
     <row r="16" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
@@ -5512,42 +5512,42 @@
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
     </row>
-    <row r="23" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:13" s="15" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
+      <c r="K23" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
     </row>
     <row r="24" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
